--- a/추가데이터_가져오기.xlsx
+++ b/추가데이터_가져오기.xlsx
@@ -413,23 +413,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1426"/>
+  <dimension ref="A1:O1541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -84086,6 +84086,6397 @@
         </is>
       </c>
     </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>(주)리얼라이즈크리에이티브</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>강병진</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr"/>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>010-3612-2547</t>
+        </is>
+      </c>
+      <c r="F1427" t="inlineStr">
+        <is>
+          <t>realiez@naver.com</t>
+        </is>
+      </c>
+      <c r="G1427" t="inlineStr"/>
+      <c r="H1427" t="inlineStr">
+        <is>
+          <t>서울시 성동구 상원12길 34, 1013호</t>
+        </is>
+      </c>
+      <c r="I1427" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1427" t="inlineStr">
+        <is>
+          <t>협력사(XR제작)</t>
+        </is>
+      </c>
+      <c r="K1427" t="inlineStr">
+        <is>
+          <t>내부담당: Charles</t>
+        </is>
+      </c>
+      <c r="L1427" t="inlineStr"/>
+      <c r="M1427" t="inlineStr">
+        <is>
+          <t>언리얼, 올인원, 단위세대, 커뮤니티, 전시, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1427" t="inlineStr">
+        <is>
+          <t>결제민감 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1427" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>승우</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>정승원</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>실장</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr"/>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>010-5034-0747</t>
+        </is>
+      </c>
+      <c r="F1428" t="inlineStr">
+        <is>
+          <t>jsw911121@gmail.com</t>
+        </is>
+      </c>
+      <c r="G1428" t="inlineStr"/>
+      <c r="H1428" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 시민대로 401, 2층 212~213</t>
+        </is>
+      </c>
+      <c r="I1428" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1428" t="inlineStr">
+        <is>
+          <t>협력사(XR제작)</t>
+        </is>
+      </c>
+      <c r="K1428" t="inlineStr"/>
+      <c r="L1428" t="inlineStr"/>
+      <c r="M1428" t="inlineStr">
+        <is>
+          <t>언리얼, 올인원, 단위세대, 커뮤니티, 전시, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1428" t="inlineStr">
+        <is>
+          <t>내규따름</t>
+        </is>
+      </c>
+      <c r="O1428" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>일도</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>조상민</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr"/>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>010-3611-0901</t>
+        </is>
+      </c>
+      <c r="F1429" t="inlineStr">
+        <is>
+          <t>illdo0213@naver.com</t>
+        </is>
+      </c>
+      <c r="G1429" t="inlineStr"/>
+      <c r="H1429" t="inlineStr">
+        <is>
+          <t>경기도 시흥시 산뒤2길 13</t>
+        </is>
+      </c>
+      <c r="I1429" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1429" t="inlineStr">
+        <is>
+          <t>협력사(XR제작)</t>
+        </is>
+      </c>
+      <c r="K1429" t="inlineStr"/>
+      <c r="L1429" t="inlineStr"/>
+      <c r="M1429" t="inlineStr">
+        <is>
+          <t>언리얼, 올인원, 단위세대, 커뮤니티, 전시, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1429" t="inlineStr">
+        <is>
+          <t>내규따름</t>
+        </is>
+      </c>
+      <c r="O1429" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>주식회사 레이존</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>구형근</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr"/>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>010-2044-6952</t>
+        </is>
+      </c>
+      <c r="F1430" t="inlineStr">
+        <is>
+          <t>khk@rayzone.co.kr</t>
+        </is>
+      </c>
+      <c r="G1430" t="inlineStr"/>
+      <c r="H1430" t="inlineStr">
+        <is>
+          <t>경기 하남시 미사대로 550 현대지식산업센터 한강미사 A238호</t>
+        </is>
+      </c>
+      <c r="I1430" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1430" t="inlineStr">
+        <is>
+          <t>협력사(XR제작)</t>
+        </is>
+      </c>
+      <c r="K1430" t="inlineStr"/>
+      <c r="L1430" t="inlineStr"/>
+      <c r="M1430" t="inlineStr">
+        <is>
+          <t>언리얼, 올인원, 신규개발, 단위세대, 커뮤니티, 전시, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1430" t="inlineStr">
+        <is>
+          <t>내규따름 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1430" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>238아뜰리에</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>이정은</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr"/>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>010-8961-3491</t>
+        </is>
+      </c>
+      <c r="F1431" t="inlineStr">
+        <is>
+          <t>2je.2mail@gmail.com</t>
+        </is>
+      </c>
+      <c r="G1431" t="inlineStr"/>
+      <c r="H1431" t="inlineStr">
+        <is>
+          <t>서울시 서초구 동작대로 62</t>
+        </is>
+      </c>
+      <c r="I1431" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1431" t="inlineStr">
+        <is>
+          <t>협력사(XR제작),협력사(CG)</t>
+        </is>
+      </c>
+      <c r="K1431" t="inlineStr"/>
+      <c r="L1431" t="inlineStr"/>
+      <c r="M1431" t="inlineStr">
+        <is>
+          <t>언리얼, 도면기반공간, 단위세대, 커뮤니티, 전시, 국내(개인), 도면, 제작, 건축CG</t>
+        </is>
+      </c>
+      <c r="N1431" t="inlineStr">
+        <is>
+          <t>내규따름 / 퇴사 인원</t>
+        </is>
+      </c>
+      <c r="O1431" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>노소정</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>노소정</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>프리</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr"/>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>010-6542-9523</t>
+        </is>
+      </c>
+      <c r="F1432" t="inlineStr">
+        <is>
+          <t>sjroh98@gmail.com</t>
+        </is>
+      </c>
+      <c r="G1432" t="inlineStr"/>
+      <c r="H1432" t="inlineStr">
+        <is>
+          <t>서울 은평구 갈현로11길 46, 103동 1401호</t>
+        </is>
+      </c>
+      <c r="I1432" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1432" t="inlineStr">
+        <is>
+          <t>협력사(XR제작)</t>
+        </is>
+      </c>
+      <c r="K1432" t="inlineStr"/>
+      <c r="L1432" t="inlineStr"/>
+      <c r="M1432" t="inlineStr">
+        <is>
+          <t>언리얼, 제작, 단위세대, 커뮤니티, 전시, 개인(프리랜서)</t>
+        </is>
+      </c>
+      <c r="N1432" t="inlineStr">
+        <is>
+          <t>내규따름</t>
+        </is>
+      </c>
+      <c r="O1432" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>GOVR</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>이태현</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr"/>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>010-9460-1312</t>
+        </is>
+      </c>
+      <c r="F1433" t="inlineStr">
+        <is>
+          <t>GOVR360@gmail.com</t>
+        </is>
+      </c>
+      <c r="G1433" t="inlineStr"/>
+      <c r="H1433" t="inlineStr">
+        <is>
+          <t>서울특별시 마포구 월드컵북로 396,누리꿈스퀘어 연구개발타워 1105-11호</t>
+        </is>
+      </c>
+      <c r="I1433" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1433" t="inlineStr">
+        <is>
+          <t>협력사(XR제작)</t>
+        </is>
+      </c>
+      <c r="K1433" t="inlineStr"/>
+      <c r="L1433" t="inlineStr"/>
+      <c r="M1433" t="inlineStr">
+        <is>
+          <t>언리얼, 유니티</t>
+        </is>
+      </c>
+      <c r="N1433" t="inlineStr"/>
+      <c r="O1433" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>에이에스피 이미지(ASP IMAGE)</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>신건주</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr"/>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>010-3114-8150</t>
+        </is>
+      </c>
+      <c r="F1434" t="inlineStr"/>
+      <c r="G1434" t="inlineStr"/>
+      <c r="H1434" t="inlineStr">
+        <is>
+          <t>서울 도봉구 도봉로 517 3층 5호</t>
+        </is>
+      </c>
+      <c r="I1434" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1434" t="inlineStr">
+        <is>
+          <t>협력사(촬영)</t>
+        </is>
+      </c>
+      <c r="K1434" t="inlineStr"/>
+      <c r="L1434" t="inlineStr"/>
+      <c r="M1434" t="inlineStr">
+        <is>
+          <t>드론, 지상360촬영, 드론촬영, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1434" t="inlineStr"/>
+      <c r="O1434" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>애드어드론</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>강주성</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr"/>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>010-6308-8614</t>
+        </is>
+      </c>
+      <c r="F1435" t="inlineStr">
+        <is>
+          <t>add.a.drone1@gmail.com</t>
+        </is>
+      </c>
+      <c r="G1435" t="inlineStr"/>
+      <c r="H1435" t="inlineStr"/>
+      <c r="I1435" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1435" t="inlineStr">
+        <is>
+          <t>협력사(촬영)</t>
+        </is>
+      </c>
+      <c r="K1435" t="inlineStr"/>
+      <c r="L1435" t="inlineStr"/>
+      <c r="M1435" t="inlineStr">
+        <is>
+          <t>드론, 드론촬영, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1435" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1435" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>스카이블루버드</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>김진현</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr"/>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>010-3796-6364</t>
+        </is>
+      </c>
+      <c r="F1436" t="inlineStr">
+        <is>
+          <t>skybluebird_official@naver.com</t>
+        </is>
+      </c>
+      <c r="G1436" t="inlineStr"/>
+      <c r="H1436" t="inlineStr">
+        <is>
+          <t>서울 강서구 마곡중앙6로 11 (마곡동) 913호</t>
+        </is>
+      </c>
+      <c r="I1436" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1436" t="inlineStr">
+        <is>
+          <t>협력사(촬영)</t>
+        </is>
+      </c>
+      <c r="K1436" t="inlineStr"/>
+      <c r="L1436" t="inlineStr"/>
+      <c r="M1436" t="inlineStr">
+        <is>
+          <t>드론, 드론촬영, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1436" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1436" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>프라임파노라마</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>정현철</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr"/>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>010-8880-4846</t>
+        </is>
+      </c>
+      <c r="F1437" t="inlineStr">
+        <is>
+          <t>primepano@naver.com</t>
+        </is>
+      </c>
+      <c r="G1437" t="inlineStr"/>
+      <c r="H1437" t="inlineStr">
+        <is>
+          <t>경기 안양시 동안구 시민대로327번길 11-41, 505호</t>
+        </is>
+      </c>
+      <c r="I1437" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1437" t="inlineStr">
+        <is>
+          <t>협력사(촬영)</t>
+        </is>
+      </c>
+      <c r="K1437" t="inlineStr"/>
+      <c r="L1437" t="inlineStr"/>
+      <c r="M1437" t="inlineStr">
+        <is>
+          <t>지상촬영, 드론촬영, 지상360촬영, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1437" t="inlineStr"/>
+      <c r="O1437" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>소프트히어로</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>백창훤</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr"/>
+      <c r="E1438" t="inlineStr">
+        <is>
+          <t>0.50407782173</t>
+        </is>
+      </c>
+      <c r="F1438" t="inlineStr"/>
+      <c r="G1438" t="inlineStr"/>
+      <c r="H1438" t="inlineStr">
+        <is>
+          <t>서울 구로구 경인로 572, 208,209호 6호</t>
+        </is>
+      </c>
+      <c r="I1438" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1438" t="inlineStr">
+        <is>
+          <t>협력사(촬영)</t>
+        </is>
+      </c>
+      <c r="K1438" t="inlineStr"/>
+      <c r="L1438" t="inlineStr"/>
+      <c r="M1438" t="inlineStr">
+        <is>
+          <t>지상촬영, 지상360촬영, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1438" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1438" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>(주)이머스</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>김민구</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr"/>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>010-6366-3645</t>
+        </is>
+      </c>
+      <c r="F1439" t="inlineStr">
+        <is>
+          <t>mg@immerse.co.kr</t>
+        </is>
+      </c>
+      <c r="G1439" t="inlineStr"/>
+      <c r="H1439" t="inlineStr">
+        <is>
+          <t>서울 금천구 가산디지털 2로 173 에이스비즈포레 302</t>
+        </is>
+      </c>
+      <c r="I1439" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1439" t="inlineStr">
+        <is>
+          <t>협력사(촬영)</t>
+        </is>
+      </c>
+      <c r="K1439" t="inlineStr"/>
+      <c r="L1439" t="inlineStr"/>
+      <c r="M1439" t="inlineStr">
+        <is>
+          <t>메타포트, 올인원, 지상360촬영, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1439" t="inlineStr"/>
+      <c r="O1439" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>드로니</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>정원우</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>실장</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr"/>
+      <c r="E1440" t="inlineStr">
+        <is>
+          <t>010-4106-7947</t>
+        </is>
+      </c>
+      <c r="F1440" t="inlineStr">
+        <is>
+          <t>m16a6@naver.com</t>
+        </is>
+      </c>
+      <c r="G1440" t="inlineStr"/>
+      <c r="H1440" t="inlineStr"/>
+      <c r="I1440" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1440" t="inlineStr">
+        <is>
+          <t>협력사(촬영)</t>
+        </is>
+      </c>
+      <c r="K1440" t="inlineStr"/>
+      <c r="L1440" t="inlineStr"/>
+      <c r="M1440" t="inlineStr">
+        <is>
+          <t>드론촬영, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1440" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)(링크)</t>
+        </is>
+      </c>
+      <c r="O1440" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>S&amp;H</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>이희병</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr"/>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>010-5235-3097</t>
+        </is>
+      </c>
+      <c r="F1441" t="inlineStr">
+        <is>
+          <t>heliphoto@hanmail.net</t>
+        </is>
+      </c>
+      <c r="G1441" t="inlineStr"/>
+      <c r="H1441" t="inlineStr">
+        <is>
+          <t>서울시 성동구 성수일로 10, 402-1호</t>
+        </is>
+      </c>
+      <c r="I1441" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1441" t="inlineStr">
+        <is>
+          <t>협력사(촬영)</t>
+        </is>
+      </c>
+      <c r="K1441" t="inlineStr">
+        <is>
+          <t>내부담당: Charles</t>
+        </is>
+      </c>
+      <c r="L1441" t="inlineStr"/>
+      <c r="M1441" t="inlineStr">
+        <is>
+          <t>드론, 드론촬영, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1441" t="inlineStr"/>
+      <c r="O1441" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>OK항공촬영</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>양해운</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr"/>
+      <c r="E1442" t="inlineStr">
+        <is>
+          <t>010-8205-3070</t>
+        </is>
+      </c>
+      <c r="F1442" t="inlineStr">
+        <is>
+          <t>okhelicam0@naver.com</t>
+        </is>
+      </c>
+      <c r="G1442" t="inlineStr"/>
+      <c r="H1442" t="inlineStr">
+        <is>
+          <t>서울특별시용산구백범로263,1층(효창동)</t>
+        </is>
+      </c>
+      <c r="I1442" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1442" t="inlineStr">
+        <is>
+          <t>협력사(촬영)</t>
+        </is>
+      </c>
+      <c r="K1442" t="inlineStr">
+        <is>
+          <t>내부담당: Charles</t>
+        </is>
+      </c>
+      <c r="L1442" t="inlineStr"/>
+      <c r="M1442" t="inlineStr">
+        <is>
+          <t>드론, 드론촬영, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1442" t="inlineStr"/>
+      <c r="O1442" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>주식회사 디자인엔틱</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>채수남</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr"/>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>010-7141-7375</t>
+        </is>
+      </c>
+      <c r="F1443" t="inlineStr">
+        <is>
+          <t>upper3d@naver.com</t>
+        </is>
+      </c>
+      <c r="G1443" t="inlineStr"/>
+      <c r="H1443" t="inlineStr"/>
+      <c r="I1443" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1443" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1443" t="inlineStr"/>
+      <c r="L1443" t="inlineStr"/>
+      <c r="M1443" t="inlineStr">
+        <is>
+          <t>올인원, 건축영상, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1443" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1443" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>주식회사 디케이블루</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>유재현</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr"/>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>010-9495-8832</t>
+        </is>
+      </c>
+      <c r="F1444" t="inlineStr">
+        <is>
+          <t>dk@dkblue.co.kr</t>
+        </is>
+      </c>
+      <c r="G1444" t="inlineStr"/>
+      <c r="H1444" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대장동 576-4 B1F</t>
+        </is>
+      </c>
+      <c r="I1444" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1444" t="inlineStr">
+        <is>
+          <t>협력사(영상),협력사(OPN)</t>
+        </is>
+      </c>
+      <c r="K1444" t="inlineStr"/>
+      <c r="L1444" t="inlineStr"/>
+      <c r="M1444" t="inlineStr">
+        <is>
+          <t>건축, 건축영상, 국내(법인), 여성기업</t>
+        </is>
+      </c>
+      <c r="N1444" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1444" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>애니민스튜디오</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>박중민</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr"/>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>010-2016-0756</t>
+        </is>
+      </c>
+      <c r="F1445" t="inlineStr">
+        <is>
+          <t>atspin@naver.com</t>
+        </is>
+      </c>
+      <c r="G1445" t="inlineStr"/>
+      <c r="H1445" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 송파대로 201</t>
+        </is>
+      </c>
+      <c r="I1445" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1445" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1445" t="inlineStr"/>
+      <c r="L1445" t="inlineStr"/>
+      <c r="M1445" t="inlineStr">
+        <is>
+          <t>건축영상, 고퀄리티, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1445" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1445" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>이맥시스</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>진원용</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr"/>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>010-9654-9080</t>
+        </is>
+      </c>
+      <c r="F1446" t="inlineStr">
+        <is>
+          <t>wychin@imaxis.co.kr</t>
+        </is>
+      </c>
+      <c r="G1446" t="inlineStr"/>
+      <c r="H1446" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 송파대로 201</t>
+        </is>
+      </c>
+      <c r="I1446" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1446" t="inlineStr">
+        <is>
+          <t>협력사(영상),협력사(CG)</t>
+        </is>
+      </c>
+      <c r="K1446" t="inlineStr"/>
+      <c r="L1446" t="inlineStr"/>
+      <c r="M1446" t="inlineStr">
+        <is>
+          <t>건축영상, 국내(법인), 건축CG</t>
+        </is>
+      </c>
+      <c r="N1446" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1446" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>제이디스튜디오</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>김정두</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr"/>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>010-4232-3847</t>
+        </is>
+      </c>
+      <c r="F1447" t="inlineStr">
+        <is>
+          <t>rlacnseka@naver.com</t>
+        </is>
+      </c>
+      <c r="G1447" t="inlineStr"/>
+      <c r="H1447" t="inlineStr">
+        <is>
+          <t>서울 관악구 은천로 51, 7층</t>
+        </is>
+      </c>
+      <c r="I1447" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1447" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1447" t="inlineStr"/>
+      <c r="L1447" t="inlineStr"/>
+      <c r="M1447" t="inlineStr">
+        <is>
+          <t>건축, 미디어아트, 건축영상, 미디어아트, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1447" t="inlineStr">
+        <is>
+          <t>0.0 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1447" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>필름팩토리</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>이시형</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr"/>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>010-3282-5954</t>
+        </is>
+      </c>
+      <c r="F1448" t="inlineStr">
+        <is>
+          <t>seetv0522@naver.com</t>
+        </is>
+      </c>
+      <c r="G1448" t="inlineStr"/>
+      <c r="H1448" t="inlineStr"/>
+      <c r="I1448" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1448" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1448" t="inlineStr"/>
+      <c r="L1448" t="inlineStr"/>
+      <c r="M1448" t="inlineStr">
+        <is>
+          <t>기획, 건축영상, 건축영상, 홍보영상, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1448" t="inlineStr"/>
+      <c r="O1448" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>모션프로덕션</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>김경은</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr"/>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>010-4723-3076</t>
+        </is>
+      </c>
+      <c r="F1449" t="inlineStr">
+        <is>
+          <t>film@cgmotion.net</t>
+        </is>
+      </c>
+      <c r="G1449" t="inlineStr"/>
+      <c r="H1449" t="inlineStr"/>
+      <c r="I1449" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1449" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1449" t="inlineStr"/>
+      <c r="L1449" t="inlineStr"/>
+      <c r="M1449" t="inlineStr">
+        <is>
+          <t>기획, 건축영상, 건축영상, 홍보영상, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1449" t="inlineStr"/>
+      <c r="O1449" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>저니마치</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>이한준</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr"/>
+      <c r="E1450" t="inlineStr">
+        <is>
+          <t>010-4723-3076</t>
+        </is>
+      </c>
+      <c r="F1450" t="inlineStr">
+        <is>
+          <t>journey@journeymarch.com</t>
+        </is>
+      </c>
+      <c r="G1450" t="inlineStr"/>
+      <c r="H1450" t="inlineStr"/>
+      <c r="I1450" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1450" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1450" t="inlineStr"/>
+      <c r="L1450" t="inlineStr"/>
+      <c r="M1450" t="inlineStr">
+        <is>
+          <t>VFX, 후디니, 캐릭터, 아나몰픽, 미디어아트, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1450" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1450" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>코드스토리</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>조정은</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr"/>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>010-8449-5189</t>
+        </is>
+      </c>
+      <c r="F1451" t="inlineStr">
+        <is>
+          <t>biz@codestory.biz</t>
+        </is>
+      </c>
+      <c r="G1451" t="inlineStr"/>
+      <c r="H1451" t="inlineStr"/>
+      <c r="I1451" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1451" t="inlineStr">
+        <is>
+          <t>협력사(영상),협력사(OPN)</t>
+        </is>
+      </c>
+      <c r="K1451" t="inlineStr"/>
+      <c r="L1451" t="inlineStr"/>
+      <c r="M1451" t="inlineStr">
+        <is>
+          <t>아나몰픽, 캐릭터, VR, 미디어아트, 국내(법인), 여성기업</t>
+        </is>
+      </c>
+      <c r="N1451" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1451" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>뉴작</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>정해현</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr"/>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>010-4743-2420</t>
+        </is>
+      </c>
+      <c r="F1452" t="inlineStr">
+        <is>
+          <t>ceo@newjak.ne</t>
+        </is>
+      </c>
+      <c r="G1452" t="inlineStr"/>
+      <c r="H1452" t="inlineStr"/>
+      <c r="I1452" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1452" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1452" t="inlineStr">
+        <is>
+          <t>내부담당: Charles</t>
+        </is>
+      </c>
+      <c r="L1452" t="inlineStr"/>
+      <c r="M1452" t="inlineStr">
+        <is>
+          <t>미디어아트, 언리얼기반, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1452" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1452" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>엔토닉크리에이티브</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>강석모</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr"/>
+      <c r="E1453" t="inlineStr">
+        <is>
+          <t>010-6579-1759</t>
+        </is>
+      </c>
+      <c r="F1453" t="inlineStr">
+        <is>
+          <t>credit@ntonic.com</t>
+        </is>
+      </c>
+      <c r="G1453" t="inlineStr"/>
+      <c r="H1453" t="inlineStr">
+        <is>
+          <t>서울 강남구 논현로18길 11, 4층 401호(개포동, 제일빌딩)</t>
+        </is>
+      </c>
+      <c r="I1453" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1453" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1453" t="inlineStr">
+        <is>
+          <t>내부담당: Charles</t>
+        </is>
+      </c>
+      <c r="L1453" t="inlineStr"/>
+      <c r="M1453" t="inlineStr">
+        <is>
+          <t>미디어아트, 언리얼기반, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1453" t="inlineStr">
+        <is>
+          <t>k-컬쳐 컨소시엄 업체 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1453" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>the1991</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr"/>
+      <c r="C1454" t="inlineStr"/>
+      <c r="D1454" t="inlineStr"/>
+      <c r="E1454" t="inlineStr"/>
+      <c r="F1454" t="inlineStr"/>
+      <c r="G1454" t="inlineStr"/>
+      <c r="H1454" t="inlineStr"/>
+      <c r="I1454" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1454" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1454" t="inlineStr">
+        <is>
+          <t>내부담당: Charles</t>
+        </is>
+      </c>
+      <c r="L1454" t="inlineStr"/>
+      <c r="M1454" t="inlineStr">
+        <is>
+          <t>미디어아트, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1454" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1454" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>CUZ</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>진실</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr"/>
+      <c r="E1455" t="inlineStr">
+        <is>
+          <t>070-8095-2401</t>
+        </is>
+      </c>
+      <c r="F1455" t="inlineStr">
+        <is>
+          <t>contact@cuz-art.com</t>
+        </is>
+      </c>
+      <c r="G1455" t="inlineStr"/>
+      <c r="H1455" t="inlineStr">
+        <is>
+          <t>서울 강남구 역삼로 157, 5층 (정평 빌딩)</t>
+        </is>
+      </c>
+      <c r="I1455" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1455" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1455" t="inlineStr"/>
+      <c r="L1455" t="inlineStr"/>
+      <c r="M1455" t="inlineStr">
+        <is>
+          <t>미디어아트, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1455" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1455" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>비브스튜디오</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>김세규</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr"/>
+      <c r="E1456" t="inlineStr">
+        <is>
+          <t>02-574-7076</t>
+        </is>
+      </c>
+      <c r="F1456" t="inlineStr">
+        <is>
+          <t>info@vivestudios.com</t>
+        </is>
+      </c>
+      <c r="G1456" t="inlineStr"/>
+      <c r="H1456" t="inlineStr">
+        <is>
+          <t>서울 강남구 언주로 727 4층</t>
+        </is>
+      </c>
+      <c r="I1456" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1456" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1456" t="inlineStr"/>
+      <c r="L1456" t="inlineStr"/>
+      <c r="M1456" t="inlineStr">
+        <is>
+          <t>미디어아트, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1456" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1456" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>후 스튜디오</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>김민성</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr"/>
+      <c r="E1457" t="inlineStr">
+        <is>
+          <t>010-2469-6279</t>
+        </is>
+      </c>
+      <c r="F1457" t="inlineStr">
+        <is>
+          <t>whoizhoo@gmail.com</t>
+        </is>
+      </c>
+      <c r="G1457" t="inlineStr"/>
+      <c r="H1457" t="inlineStr">
+        <is>
+          <t>서울 서대문구 충정로 50, 1104호 (충정로3가)</t>
+        </is>
+      </c>
+      <c r="I1457" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1457" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1457" t="inlineStr"/>
+      <c r="L1457" t="inlineStr"/>
+      <c r="M1457" t="inlineStr">
+        <is>
+          <t>미디어아트, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1457" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1457" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>어썸뷰</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>유성운</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr"/>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>1551-9930</t>
+        </is>
+      </c>
+      <c r="F1458" t="inlineStr">
+        <is>
+          <t>awesomeview@awesomeisland.co.kr</t>
+        </is>
+      </c>
+      <c r="G1458" t="inlineStr"/>
+      <c r="H1458" t="inlineStr">
+        <is>
+          <t>서울 강서구 양천로 583, B동 706호~707호</t>
+        </is>
+      </c>
+      <c r="I1458" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1458" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1458" t="inlineStr"/>
+      <c r="L1458" t="inlineStr"/>
+      <c r="M1458" t="inlineStr">
+        <is>
+          <t>미디어아트, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1458" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1458" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>엠앤케이</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>김원상</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr"/>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>1566-5653</t>
+        </is>
+      </c>
+      <c r="F1459" t="inlineStr">
+        <is>
+          <t>cs@themnk.co.kr</t>
+        </is>
+      </c>
+      <c r="G1459" t="inlineStr"/>
+      <c r="H1459" t="inlineStr">
+        <is>
+          <t>광주 동구 칠전길 2</t>
+        </is>
+      </c>
+      <c r="I1459" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1459" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1459" t="inlineStr"/>
+      <c r="L1459" t="inlineStr"/>
+      <c r="M1459" t="inlineStr">
+        <is>
+          <t>미디어아트, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1459" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1459" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>더그림 미디어</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>황희승</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr"/>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>02-993-2257</t>
+        </is>
+      </c>
+      <c r="F1460" t="inlineStr">
+        <is>
+          <t>color@thegream.com</t>
+        </is>
+      </c>
+      <c r="G1460" t="inlineStr"/>
+      <c r="H1460" t="inlineStr">
+        <is>
+          <t>경기 용인시 기흥구 흥덕2로 117번길 19</t>
+        </is>
+      </c>
+      <c r="I1460" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1460" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1460" t="inlineStr"/>
+      <c r="L1460" t="inlineStr"/>
+      <c r="M1460" t="inlineStr">
+        <is>
+          <t>미디어아트, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1460" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1460" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>에이플랜컴퍼니</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>김현호</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr"/>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>02-981-9334</t>
+        </is>
+      </c>
+      <c r="F1461" t="inlineStr">
+        <is>
+          <t>aplan0458@naver.com</t>
+        </is>
+      </c>
+      <c r="G1461" t="inlineStr"/>
+      <c r="H1461" t="inlineStr">
+        <is>
+          <t>서울 마포구 잔다리로 28 W&amp;H빌딩 4F</t>
+        </is>
+      </c>
+      <c r="I1461" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1461" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1461" t="inlineStr"/>
+      <c r="L1461" t="inlineStr"/>
+      <c r="M1461" t="inlineStr">
+        <is>
+          <t>미디어아트, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1461" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1461" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>덱스터 스튜디오</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>김용화</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr"/>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>02-6391-7000</t>
+        </is>
+      </c>
+      <c r="F1462" t="inlineStr">
+        <is>
+          <t>dexterstudios@dexterstudios.com</t>
+        </is>
+      </c>
+      <c r="G1462" t="inlineStr"/>
+      <c r="H1462" t="inlineStr">
+        <is>
+          <t>서울 마포구 매봉산로 75 동아디지털미디어센터 DDMC 18/19층</t>
+        </is>
+      </c>
+      <c r="I1462" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1462" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1462" t="inlineStr"/>
+      <c r="L1462" t="inlineStr"/>
+      <c r="M1462" t="inlineStr">
+        <is>
+          <t>미디어아트, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1462" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1462" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>봄랩</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>신재희</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr"/>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>02-6405-0318</t>
+        </is>
+      </c>
+      <c r="F1463" t="inlineStr">
+        <is>
+          <t>info@vomlab.com</t>
+        </is>
+      </c>
+      <c r="G1463" t="inlineStr"/>
+      <c r="H1463" t="inlineStr">
+        <is>
+          <t>서울 성북구 돌곶이로 32, 3층</t>
+        </is>
+      </c>
+      <c r="I1463" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1463" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1463" t="inlineStr"/>
+      <c r="L1463" t="inlineStr"/>
+      <c r="M1463" t="inlineStr">
+        <is>
+          <t>미디어아트, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1463" t="inlineStr">
+        <is>
+          <t>2025 K-컬쳐 입찰 참여 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1463" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>올인원디자인</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>정수인</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr"/>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>010-2322-4356</t>
+        </is>
+      </c>
+      <c r="F1464" t="inlineStr">
+        <is>
+          <t>allinone_design@daum.net</t>
+        </is>
+      </c>
+      <c r="G1464" t="inlineStr"/>
+      <c r="H1464" t="inlineStr">
+        <is>
+          <t>서울시 중랑구 면목로 96길 25</t>
+        </is>
+      </c>
+      <c r="I1464" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1464" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1464" t="inlineStr"/>
+      <c r="L1464" t="inlineStr"/>
+      <c r="M1464" t="inlineStr">
+        <is>
+          <t>2D, 미디어아트, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1464" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1464" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>디보프로덕션</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>윤희광</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr"/>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>010-8489-0284</t>
+        </is>
+      </c>
+      <c r="F1465" t="inlineStr">
+        <is>
+          <t>newhappy0107@gmail.com</t>
+        </is>
+      </c>
+      <c r="G1465" t="inlineStr"/>
+      <c r="H1465" t="inlineStr">
+        <is>
+          <t>서울 금천구 서부샛길 606 대성디폴리스 B동 2508</t>
+        </is>
+      </c>
+      <c r="I1465" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1465" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1465" t="inlineStr"/>
+      <c r="L1465" t="inlineStr"/>
+      <c r="M1465" t="inlineStr">
+        <is>
+          <t>VFX, 영화, 편집, 미디어아트, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1465" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1465" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>터프쿠키</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>김요한</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr"/>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>010-2544-1344</t>
+        </is>
+      </c>
+      <c r="F1466" t="inlineStr">
+        <is>
+          <t>gunky1@naver.com</t>
+        </is>
+      </c>
+      <c r="G1466" t="inlineStr"/>
+      <c r="H1466" t="inlineStr">
+        <is>
+          <t>경기 구리시 건원대로 42</t>
+        </is>
+      </c>
+      <c r="I1466" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1466" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1466" t="inlineStr"/>
+      <c r="L1466" t="inlineStr"/>
+      <c r="M1466" t="inlineStr">
+        <is>
+          <t>VFX, 미디어아트, 3D, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1466" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1466" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>멜리그래픽</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>박수연</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr"/>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>010-6636-7847</t>
+        </is>
+      </c>
+      <c r="F1467" t="inlineStr">
+        <is>
+          <t>melligraphic@naver.com</t>
+        </is>
+      </c>
+      <c r="G1467" t="inlineStr"/>
+      <c r="H1467" t="inlineStr">
+        <is>
+          <t>서울 구로구 개봉로 11길, 38-3</t>
+        </is>
+      </c>
+      <c r="I1467" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1467" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1467" t="inlineStr"/>
+      <c r="L1467" t="inlineStr"/>
+      <c r="M1467" t="inlineStr">
+        <is>
+          <t>3D, 미디어아트, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1467" t="inlineStr"/>
+      <c r="O1467" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>오프더빌리지</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>현준</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr"/>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>010-4179-9807</t>
+        </is>
+      </c>
+      <c r="F1468" t="inlineStr">
+        <is>
+          <t>jun@ofthervillage.com</t>
+        </is>
+      </c>
+      <c r="G1468" t="inlineStr"/>
+      <c r="H1468" t="inlineStr">
+        <is>
+          <t>서울 동작구 남부순환로 2043, 3층</t>
+        </is>
+      </c>
+      <c r="I1468" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1468" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1468" t="inlineStr"/>
+      <c r="L1468" t="inlineStr"/>
+      <c r="M1468" t="inlineStr">
+        <is>
+          <t>미디어아트, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1468" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1468" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>김예찬</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>김예찬</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr"/>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>010-5099-0480</t>
+        </is>
+      </c>
+      <c r="F1469" t="inlineStr">
+        <is>
+          <t>kimyechan2@naver.com</t>
+        </is>
+      </c>
+      <c r="G1469" t="inlineStr"/>
+      <c r="H1469" t="inlineStr"/>
+      <c r="I1469" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1469" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1469" t="inlineStr"/>
+      <c r="L1469" t="inlineStr"/>
+      <c r="M1469" t="inlineStr">
+        <is>
+          <t>미디어아트, 모션그래픽, 캐릭터, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1469" t="inlineStr"/>
+      <c r="O1469" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>애니멀블루</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>이혜상</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr"/>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>010-5054-3720</t>
+        </is>
+      </c>
+      <c r="F1470" t="inlineStr">
+        <is>
+          <t>001@animalblue.net</t>
+        </is>
+      </c>
+      <c r="G1470" t="inlineStr"/>
+      <c r="H1470" t="inlineStr">
+        <is>
+          <t>서울 강남구 테헤란로 310 1412호</t>
+        </is>
+      </c>
+      <c r="I1470" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1470" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1470" t="inlineStr"/>
+      <c r="L1470" t="inlineStr"/>
+      <c r="M1470" t="inlineStr">
+        <is>
+          <t>기획, 홍보영상, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1470" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1470" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>VERS</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>심상훈</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr"/>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>02-512-0982</t>
+        </is>
+      </c>
+      <c r="F1471" t="inlineStr">
+        <is>
+          <t>shim@vers.kr</t>
+        </is>
+      </c>
+      <c r="G1471" t="inlineStr"/>
+      <c r="H1471" t="inlineStr">
+        <is>
+          <t>서울시 서초구 서초대로 396 3층, 319호</t>
+        </is>
+      </c>
+      <c r="I1471" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1471" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1471" t="inlineStr"/>
+      <c r="L1471" t="inlineStr"/>
+      <c r="M1471" t="inlineStr">
+        <is>
+          <t>미디어아트, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1471" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1471" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>크리에이티브모루</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>안치영</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>대리</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr"/>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>010-9703-5361</t>
+        </is>
+      </c>
+      <c r="F1472" t="inlineStr">
+        <is>
+          <t>icy@cmorrow.co.kr</t>
+        </is>
+      </c>
+      <c r="G1472" t="inlineStr"/>
+      <c r="H1472" t="inlineStr">
+        <is>
+          <t>서울특별시 서초구 신반포로 45길 9-4, 더원빌딩 4층</t>
+        </is>
+      </c>
+      <c r="I1472" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1472" t="inlineStr">
+        <is>
+          <t>협력사(영상)</t>
+        </is>
+      </c>
+      <c r="K1472" t="inlineStr"/>
+      <c r="L1472" t="inlineStr"/>
+      <c r="M1472" t="inlineStr">
+        <is>
+          <t>미디어아트</t>
+        </is>
+      </c>
+      <c r="N1472" t="inlineStr">
+        <is>
+          <t>k-컬쳐 25년 사업 진행 회사 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1472" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>네오플랜스튜디오</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>이영하</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr"/>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>010-7788-7329</t>
+        </is>
+      </c>
+      <c r="F1473" t="inlineStr">
+        <is>
+          <t>puro00@naver.com</t>
+        </is>
+      </c>
+      <c r="G1473" t="inlineStr"/>
+      <c r="H1473" t="inlineStr"/>
+      <c r="I1473" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1473" t="inlineStr">
+        <is>
+          <t>협력사(CG)</t>
+        </is>
+      </c>
+      <c r="K1473" t="inlineStr"/>
+      <c r="L1473" t="inlineStr"/>
+      <c r="M1473" t="inlineStr">
+        <is>
+          <t>건축, 건축CG, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1473" t="inlineStr"/>
+      <c r="O1473" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>렌즈디오</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>위두환</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr"/>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>010-8707-9021</t>
+        </is>
+      </c>
+      <c r="F1474" t="inlineStr">
+        <is>
+          <t>renzdio@renzdio.com</t>
+        </is>
+      </c>
+      <c r="G1474" t="inlineStr"/>
+      <c r="H1474" t="inlineStr"/>
+      <c r="I1474" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1474" t="inlineStr">
+        <is>
+          <t>협력사(CG)</t>
+        </is>
+      </c>
+      <c r="K1474" t="inlineStr"/>
+      <c r="L1474" t="inlineStr"/>
+      <c r="M1474" t="inlineStr">
+        <is>
+          <t>건축, 건축CG, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1474" t="inlineStr"/>
+      <c r="O1474" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>트리박스</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>김진아</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr"/>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>010-5358-7555</t>
+        </is>
+      </c>
+      <c r="F1475" t="inlineStr">
+        <is>
+          <t>bandits1129@nate.com</t>
+        </is>
+      </c>
+      <c r="G1475" t="inlineStr"/>
+      <c r="H1475" t="inlineStr">
+        <is>
+          <t>서울시 강서구 강서로 385 우성에스비타워 1005호</t>
+        </is>
+      </c>
+      <c r="I1475" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1475" t="inlineStr">
+        <is>
+          <t>협력사(CG)</t>
+        </is>
+      </c>
+      <c r="K1475" t="inlineStr"/>
+      <c r="L1475" t="inlineStr"/>
+      <c r="M1475" t="inlineStr">
+        <is>
+          <t>건축, 건축CG, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1475" t="inlineStr"/>
+      <c r="O1475" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>아이포커스</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>유종호</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>이사</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr"/>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>010-6490-4682</t>
+        </is>
+      </c>
+      <c r="F1476" t="inlineStr">
+        <is>
+          <t>yjh@i-focus.co.kr</t>
+        </is>
+      </c>
+      <c r="G1476" t="inlineStr"/>
+      <c r="H1476" t="inlineStr">
+        <is>
+          <t>서울특별시 금천구 남부순환로 1274, B동 901호</t>
+        </is>
+      </c>
+      <c r="I1476" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1476" t="inlineStr">
+        <is>
+          <t>협력사(CG)</t>
+        </is>
+      </c>
+      <c r="K1476" t="inlineStr"/>
+      <c r="L1476" t="inlineStr"/>
+      <c r="M1476" t="inlineStr">
+        <is>
+          <t>건축CG, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1476" t="inlineStr"/>
+      <c r="O1476" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>CG Holic</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr"/>
+      <c r="C1477" t="inlineStr"/>
+      <c r="D1477" t="inlineStr"/>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>070-8273-3692</t>
+        </is>
+      </c>
+      <c r="F1477" t="inlineStr"/>
+      <c r="G1477" t="inlineStr"/>
+      <c r="H1477" t="inlineStr"/>
+      <c r="I1477" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1477" t="inlineStr">
+        <is>
+          <t>협력사(CG)</t>
+        </is>
+      </c>
+      <c r="K1477" t="inlineStr"/>
+      <c r="L1477" t="inlineStr"/>
+      <c r="M1477" t="inlineStr">
+        <is>
+          <t>건축CG, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1477" t="inlineStr"/>
+      <c r="O1477" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>유스디자인</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>유주아</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr"/>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>0.50437992761</t>
+        </is>
+      </c>
+      <c r="F1478" t="inlineStr"/>
+      <c r="G1478" t="inlineStr"/>
+      <c r="H1478" t="inlineStr"/>
+      <c r="I1478" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1478" t="inlineStr">
+        <is>
+          <t>협력사(CG)</t>
+        </is>
+      </c>
+      <c r="K1478" t="inlineStr">
+        <is>
+          <t>내부담당: Harly</t>
+        </is>
+      </c>
+      <c r="L1478" t="inlineStr"/>
+      <c r="M1478" t="inlineStr">
+        <is>
+          <t>앱/모바일, UI/UX, 웹디자인, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1478" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1478" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>오엠엠피플</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>이진형</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr"/>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>0.50430732887</t>
+        </is>
+      </c>
+      <c r="F1479" t="inlineStr"/>
+      <c r="G1479" t="inlineStr"/>
+      <c r="H1479" t="inlineStr"/>
+      <c r="I1479" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1479" t="inlineStr">
+        <is>
+          <t>협력사(CG)</t>
+        </is>
+      </c>
+      <c r="K1479" t="inlineStr">
+        <is>
+          <t>내부담당: Harly</t>
+        </is>
+      </c>
+      <c r="L1479" t="inlineStr"/>
+      <c r="M1479" t="inlineStr">
+        <is>
+          <t>앱/모바일, UI/UX, 웹디자인, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1479" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1479" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>엠브이픽</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>안진범</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr"/>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>070-4287-2051</t>
+        </is>
+      </c>
+      <c r="F1480" t="inlineStr">
+        <is>
+          <t>help@mvpick.net</t>
+        </is>
+      </c>
+      <c r="G1480" t="inlineStr"/>
+      <c r="H1480" t="inlineStr"/>
+      <c r="I1480" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1480" t="inlineStr">
+        <is>
+          <t>협력사(CG)</t>
+        </is>
+      </c>
+      <c r="K1480" t="inlineStr">
+        <is>
+          <t>내부담당: Harly</t>
+        </is>
+      </c>
+      <c r="L1480" t="inlineStr"/>
+      <c r="M1480" t="inlineStr">
+        <is>
+          <t>웹/앱, 개발, 올인원, 웹디자인, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1480" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1480" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>김우리</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>김우리</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr"/>
+      <c r="E1481" t="inlineStr"/>
+      <c r="F1481" t="inlineStr">
+        <is>
+          <t>uri_manon@naver.com</t>
+        </is>
+      </c>
+      <c r="G1481" t="inlineStr"/>
+      <c r="H1481" t="inlineStr"/>
+      <c r="I1481" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1481" t="inlineStr">
+        <is>
+          <t>협력사(CG)</t>
+        </is>
+      </c>
+      <c r="K1481" t="inlineStr">
+        <is>
+          <t>내부담당: Harly</t>
+        </is>
+      </c>
+      <c r="L1481" t="inlineStr"/>
+      <c r="M1481" t="inlineStr">
+        <is>
+          <t>웹/모바일, UI/UX, 웹디자인, 개인(프리랜서)</t>
+        </is>
+      </c>
+      <c r="N1481" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1481" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>지윤디자인</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>이지윤</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr"/>
+      <c r="D1482" t="inlineStr"/>
+      <c r="E1482" t="inlineStr"/>
+      <c r="F1482" t="inlineStr">
+        <is>
+          <t>wh459012@naver.com</t>
+        </is>
+      </c>
+      <c r="G1482" t="inlineStr"/>
+      <c r="H1482" t="inlineStr"/>
+      <c r="I1482" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1482" t="inlineStr">
+        <is>
+          <t>협력사(CG)</t>
+        </is>
+      </c>
+      <c r="K1482" t="inlineStr">
+        <is>
+          <t>내부담당: Harly</t>
+        </is>
+      </c>
+      <c r="L1482" t="inlineStr"/>
+      <c r="M1482" t="inlineStr">
+        <is>
+          <t>웹/모바일, UI/UX, 웹디자인, 개인(프리랜서)</t>
+        </is>
+      </c>
+      <c r="N1482" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1482" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>한주영</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>한주영</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr"/>
+      <c r="E1483" t="inlineStr"/>
+      <c r="F1483" t="inlineStr">
+        <is>
+          <t>concrete1203@icloud.com</t>
+        </is>
+      </c>
+      <c r="G1483" t="inlineStr"/>
+      <c r="H1483" t="inlineStr"/>
+      <c r="I1483" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1483" t="inlineStr">
+        <is>
+          <t>협력사(CG)</t>
+        </is>
+      </c>
+      <c r="K1483" t="inlineStr">
+        <is>
+          <t>내부담당: Harly</t>
+        </is>
+      </c>
+      <c r="L1483" t="inlineStr"/>
+      <c r="M1483" t="inlineStr">
+        <is>
+          <t>웹/앱, 인터랙티브, 콘텐츠, 웹디자인, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1483" t="inlineStr"/>
+      <c r="O1483" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>이지호</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>이지호</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>디자인</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr"/>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>010-9928-6488</t>
+        </is>
+      </c>
+      <c r="F1484" t="inlineStr"/>
+      <c r="G1484" t="inlineStr"/>
+      <c r="H1484" t="inlineStr"/>
+      <c r="I1484" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1484" t="inlineStr">
+        <is>
+          <t>협력사(CG)</t>
+        </is>
+      </c>
+      <c r="K1484" t="inlineStr"/>
+      <c r="L1484" t="inlineStr"/>
+      <c r="M1484" t="inlineStr">
+        <is>
+          <t>웹디자인, 개인(프리랜서)</t>
+        </is>
+      </c>
+      <c r="N1484" t="inlineStr">
+        <is>
+          <t>퇴사 인원</t>
+        </is>
+      </c>
+      <c r="O1484" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>김수빈</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>김수빈</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>디자인</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr"/>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>010-7378-1477</t>
+        </is>
+      </c>
+      <c r="F1485" t="inlineStr">
+        <is>
+          <t>ksb08280828@gmail.com</t>
+        </is>
+      </c>
+      <c r="G1485" t="inlineStr"/>
+      <c r="H1485" t="inlineStr"/>
+      <c r="I1485" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1485" t="inlineStr">
+        <is>
+          <t>협력사(CG)</t>
+        </is>
+      </c>
+      <c r="K1485" t="inlineStr"/>
+      <c r="L1485" t="inlineStr"/>
+      <c r="M1485" t="inlineStr">
+        <is>
+          <t>웹디자인, 개인(프리랜서)</t>
+        </is>
+      </c>
+      <c r="N1485" t="inlineStr"/>
+      <c r="O1485" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>이지윤</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>이지윤</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr"/>
+      <c r="D1486" t="inlineStr"/>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>010-4059-5452</t>
+        </is>
+      </c>
+      <c r="F1486" t="inlineStr">
+        <is>
+          <t>wh459012@naver.com</t>
+        </is>
+      </c>
+      <c r="G1486" t="inlineStr"/>
+      <c r="H1486" t="inlineStr"/>
+      <c r="I1486" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1486" t="inlineStr">
+        <is>
+          <t>협력사(CG)</t>
+        </is>
+      </c>
+      <c r="K1486" t="inlineStr"/>
+      <c r="L1486" t="inlineStr"/>
+      <c r="M1486" t="inlineStr">
+        <is>
+          <t>웹/모바일, UI/UX, 미디어아트, 개인(프리랜서)</t>
+        </is>
+      </c>
+      <c r="N1486" t="inlineStr"/>
+      <c r="O1486" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>윤종호</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>윤종호</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>실장</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr"/>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>010-4749-3932</t>
+        </is>
+      </c>
+      <c r="F1487" t="inlineStr">
+        <is>
+          <t>cube63@nate.com</t>
+        </is>
+      </c>
+      <c r="G1487" t="inlineStr"/>
+      <c r="H1487" t="inlineStr">
+        <is>
+          <t>경기도 성남시 중원구 광명로 89, B511호</t>
+        </is>
+      </c>
+      <c r="I1487" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1487" t="inlineStr">
+        <is>
+          <t>협력사(모델링)</t>
+        </is>
+      </c>
+      <c r="K1487" t="inlineStr">
+        <is>
+          <t>내부담당: Charles</t>
+        </is>
+      </c>
+      <c r="L1487" t="inlineStr"/>
+      <c r="M1487" t="inlineStr">
+        <is>
+          <t>건축, 개인(프리랜서)</t>
+        </is>
+      </c>
+      <c r="N1487" t="inlineStr">
+        <is>
+          <t>단지 사이트 제작 전문</t>
+        </is>
+      </c>
+      <c r="O1487" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>최현민</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>최현민</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>실장</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr"/>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>010-7271-6384</t>
+        </is>
+      </c>
+      <c r="F1488" t="inlineStr">
+        <is>
+          <t>freedommale3@naver.com</t>
+        </is>
+      </c>
+      <c r="G1488" t="inlineStr"/>
+      <c r="H1488" t="inlineStr"/>
+      <c r="I1488" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1488" t="inlineStr">
+        <is>
+          <t>협력사(모델링)</t>
+        </is>
+      </c>
+      <c r="K1488" t="inlineStr"/>
+      <c r="L1488" t="inlineStr"/>
+      <c r="M1488" t="inlineStr">
+        <is>
+          <t>제품, 3D 스캔, 개인(프리랜서)</t>
+        </is>
+      </c>
+      <c r="N1488" t="inlineStr">
+        <is>
+          <t>스캔, 모델링 가능 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1488" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>코랄랩스</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr"/>
+      <c r="C1489" t="inlineStr"/>
+      <c r="D1489" t="inlineStr"/>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>0507-1404-4377</t>
+        </is>
+      </c>
+      <c r="F1489" t="inlineStr">
+        <is>
+          <t>cocorallabs@gmail.com</t>
+        </is>
+      </c>
+      <c r="G1489" t="inlineStr"/>
+      <c r="H1489" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 한림대학길1 창업보육센터 12311호</t>
+        </is>
+      </c>
+      <c r="I1489" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1489" t="inlineStr">
+        <is>
+          <t>협력사(모델링)</t>
+        </is>
+      </c>
+      <c r="K1489" t="inlineStr"/>
+      <c r="L1489" t="inlineStr"/>
+      <c r="M1489" t="inlineStr">
+        <is>
+          <t>제품, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1489" t="inlineStr">
+        <is>
+          <t>홈페이지: [링크]</t>
+        </is>
+      </c>
+      <c r="O1489" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>(주)리빌더에이아이</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>송지훈</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>매니저</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr"/>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>010-6403-8159</t>
+        </is>
+      </c>
+      <c r="F1490" t="inlineStr">
+        <is>
+          <t>nic1116@rebuilderai.com</t>
+        </is>
+      </c>
+      <c r="G1490" t="inlineStr"/>
+      <c r="H1490" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로 95 (정자동) 네이버 1784</t>
+        </is>
+      </c>
+      <c r="I1490" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1490" t="inlineStr">
+        <is>
+          <t>협력사(모델링)</t>
+        </is>
+      </c>
+      <c r="K1490" t="inlineStr"/>
+      <c r="L1490" t="inlineStr"/>
+      <c r="M1490" t="inlineStr">
+        <is>
+          <t>MOU, 3D 스캔, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1490" t="inlineStr"/>
+      <c r="O1490" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>디자인사이디</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>임성윤</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr"/>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>010-9938-8562</t>
+        </is>
+      </c>
+      <c r="F1491" t="inlineStr">
+        <is>
+          <t>design@saidii.co.kr</t>
+        </is>
+      </c>
+      <c r="G1491" t="inlineStr"/>
+      <c r="H1491" t="inlineStr"/>
+      <c r="I1491" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1491" t="inlineStr">
+        <is>
+          <t>협력사(모델링)</t>
+        </is>
+      </c>
+      <c r="K1491" t="inlineStr">
+        <is>
+          <t>내부담당: Chris</t>
+        </is>
+      </c>
+      <c r="L1491" t="inlineStr"/>
+      <c r="M1491" t="inlineStr">
+        <is>
+          <t>제품, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1491" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1491" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>(주)쓰리디스튜디오모아</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>김승현</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr"/>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>010-5207-1830</t>
+        </is>
+      </c>
+      <c r="F1492" t="inlineStr">
+        <is>
+          <t>dennis@3dstudiomoa.com</t>
+        </is>
+      </c>
+      <c r="G1492" t="inlineStr"/>
+      <c r="H1492" t="inlineStr">
+        <is>
+          <t>서울시 강남구 논현로 175길 93, 3층</t>
+        </is>
+      </c>
+      <c r="I1492" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1492" t="inlineStr">
+        <is>
+          <t>협력사(모델링)</t>
+        </is>
+      </c>
+      <c r="K1492" t="inlineStr"/>
+      <c r="L1492" t="inlineStr"/>
+      <c r="M1492" t="inlineStr">
+        <is>
+          <t>3D, 3D 스캔, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1492" t="inlineStr"/>
+      <c r="O1492" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>고구려음향</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>김승곤</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr"/>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>010-9279-6921</t>
+        </is>
+      </c>
+      <c r="F1493" t="inlineStr"/>
+      <c r="G1493" t="inlineStr"/>
+      <c r="H1493" t="inlineStr"/>
+      <c r="I1493" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1493" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1493" t="inlineStr"/>
+      <c r="L1493" t="inlineStr"/>
+      <c r="M1493" t="inlineStr">
+        <is>
+          <t>디스플레이, 설치, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1493" t="inlineStr"/>
+      <c r="O1493" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>리틀록</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr"/>
+      <c r="C1494" t="inlineStr"/>
+      <c r="D1494" t="inlineStr"/>
+      <c r="E1494" t="inlineStr"/>
+      <c r="F1494" t="inlineStr"/>
+      <c r="G1494" t="inlineStr"/>
+      <c r="H1494" t="inlineStr"/>
+      <c r="I1494" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1494" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1494" t="inlineStr"/>
+      <c r="L1494" t="inlineStr"/>
+      <c r="M1494" t="inlineStr">
+        <is>
+          <t>디스플레이, 설치, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1494" t="inlineStr"/>
+      <c r="O1494" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>티지디지털</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>이예찬</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>매니저</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr"/>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>010-9088-6803</t>
+        </is>
+      </c>
+      <c r="F1495" t="inlineStr"/>
+      <c r="G1495" t="inlineStr"/>
+      <c r="H1495" t="inlineStr"/>
+      <c r="I1495" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1495" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1495" t="inlineStr"/>
+      <c r="L1495" t="inlineStr"/>
+      <c r="M1495" t="inlineStr">
+        <is>
+          <t>디스플레이, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1495" t="inlineStr"/>
+      <c r="O1495" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>주봉정보시스템(주)</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>김봉기</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr"/>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>02-555-6700</t>
+        </is>
+      </c>
+      <c r="F1496" t="inlineStr">
+        <is>
+          <t>jacob0103@joobong.net</t>
+        </is>
+      </c>
+      <c r="G1496" t="inlineStr"/>
+      <c r="H1496" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 자곡로 174-10, 강남에이스타워 G9. 322-324호</t>
+        </is>
+      </c>
+      <c r="I1496" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1496" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1496" t="inlineStr"/>
+      <c r="L1496" t="inlineStr"/>
+      <c r="M1496" t="inlineStr">
+        <is>
+          <t>사이니지, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1496" t="inlineStr">
+        <is>
+          <t>MOU 맺음 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1496" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>주식회사 삼성사이니지</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>조백석</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr"/>
+      <c r="E1497" t="inlineStr"/>
+      <c r="F1497" t="inlineStr"/>
+      <c r="G1497" t="inlineStr"/>
+      <c r="H1497" t="inlineStr">
+        <is>
+          <t>경기도 하남시 하남대로 947, 제에이동 제4층 414호</t>
+        </is>
+      </c>
+      <c r="I1497" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1497" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1497" t="inlineStr"/>
+      <c r="L1497" t="inlineStr"/>
+      <c r="M1497" t="inlineStr">
+        <is>
+          <t>키오스크, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1497" t="inlineStr"/>
+      <c r="O1497" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>(주)스마트터치</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>이인철</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr"/>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>031-765-8600</t>
+        </is>
+      </c>
+      <c r="F1498" t="inlineStr">
+        <is>
+          <t>jacob@smart-touch.co.kr</t>
+        </is>
+      </c>
+      <c r="G1498" t="inlineStr"/>
+      <c r="H1498" t="inlineStr">
+        <is>
+          <t>경기도 광주시 초월읍 무들로8번길 51-5</t>
+        </is>
+      </c>
+      <c r="I1498" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1498" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1498" t="inlineStr"/>
+      <c r="L1498" t="inlineStr"/>
+      <c r="M1498" t="inlineStr">
+        <is>
+          <t>터치모니터, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1498" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1498" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>효성 ITX</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>박재관</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>대리</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr"/>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>010-4391-7006</t>
+        </is>
+      </c>
+      <c r="F1499" t="inlineStr">
+        <is>
+          <t>jaekwan@hyosung.com</t>
+        </is>
+      </c>
+      <c r="G1499" t="inlineStr"/>
+      <c r="H1499" t="inlineStr">
+        <is>
+          <t>서울시 영등포구 선유동2로 57 15층</t>
+        </is>
+      </c>
+      <c r="I1499" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1499" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1499" t="inlineStr"/>
+      <c r="L1499" t="inlineStr"/>
+      <c r="M1499" t="inlineStr">
+        <is>
+          <t>프로젝터, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1499" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1499" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>동신패널(주)</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>윤진식</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>이사</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr"/>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>010-9013-8168</t>
+        </is>
+      </c>
+      <c r="F1500" t="inlineStr">
+        <is>
+          <t>yjs@dsindus.co.kr</t>
+        </is>
+      </c>
+      <c r="G1500" t="inlineStr"/>
+      <c r="H1500" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 흥안대로 415 동관 634호</t>
+        </is>
+      </c>
+      <c r="I1500" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1500" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1500" t="inlineStr"/>
+      <c r="L1500" t="inlineStr"/>
+      <c r="M1500" t="inlineStr">
+        <is>
+          <t>사이니지, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1500" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1500" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>플레이렌탈</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>김승환</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr"/>
+      <c r="E1501" t="inlineStr"/>
+      <c r="F1501" t="inlineStr">
+        <is>
+          <t>playrental@naver.com</t>
+        </is>
+      </c>
+      <c r="G1501" t="inlineStr"/>
+      <c r="H1501" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 백제고분로 501, 10층 1003호</t>
+        </is>
+      </c>
+      <c r="I1501" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1501" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1501" t="inlineStr"/>
+      <c r="L1501" t="inlineStr"/>
+      <c r="M1501" t="inlineStr">
+        <is>
+          <t>오큘러스, 렌탈, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1501" t="inlineStr"/>
+      <c r="O1501" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>(주)아이티플랜</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>황진석</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>부장</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr"/>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>010-8741-1570</t>
+        </is>
+      </c>
+      <c r="F1502" t="inlineStr">
+        <is>
+          <t>hjs@it-plan.co.kr</t>
+        </is>
+      </c>
+      <c r="G1502" t="inlineStr"/>
+      <c r="H1502" t="inlineStr">
+        <is>
+          <t>서울시 금천구 가산디지털1로 119 A-803</t>
+        </is>
+      </c>
+      <c r="I1502" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1502" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1502" t="inlineStr"/>
+      <c r="L1502" t="inlineStr"/>
+      <c r="M1502" t="inlineStr">
+        <is>
+          <t>데스크탑구매대행, 데스크탑, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1502" t="inlineStr"/>
+      <c r="O1502" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>한승공영</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>유승재</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>과장</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr"/>
+      <c r="E1503" t="inlineStr"/>
+      <c r="F1503" t="inlineStr">
+        <is>
+          <t>dbtmdwo@hsky.co.kr</t>
+        </is>
+      </c>
+      <c r="G1503" t="inlineStr"/>
+      <c r="H1503" t="inlineStr"/>
+      <c r="I1503" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1503" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1503" t="inlineStr"/>
+      <c r="L1503" t="inlineStr"/>
+      <c r="M1503" t="inlineStr"/>
+      <c r="N1503" t="inlineStr"/>
+      <c r="O1503" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>에스큐브랩</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr"/>
+      <c r="C1504" t="inlineStr"/>
+      <c r="D1504" t="inlineStr"/>
+      <c r="E1504" t="inlineStr"/>
+      <c r="F1504" t="inlineStr"/>
+      <c r="G1504" t="inlineStr"/>
+      <c r="H1504" t="inlineStr"/>
+      <c r="I1504" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1504" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1504" t="inlineStr"/>
+      <c r="L1504" t="inlineStr"/>
+      <c r="M1504" t="inlineStr"/>
+      <c r="N1504" t="inlineStr"/>
+      <c r="O1504" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>미디어수</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>김도형</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>팀장</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr"/>
+      <c r="E1505" t="inlineStr">
+        <is>
+          <t>010-5290-0370</t>
+        </is>
+      </c>
+      <c r="F1505" t="inlineStr">
+        <is>
+          <t>dh.kim@mediasoo.com</t>
+        </is>
+      </c>
+      <c r="G1505" t="inlineStr"/>
+      <c r="H1505" t="inlineStr">
+        <is>
+          <t>서울특별시 강서구 양천로 738 한강G트리타워 10층 1010호</t>
+        </is>
+      </c>
+      <c r="I1505" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1505" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1505" t="inlineStr"/>
+      <c r="L1505" t="inlineStr"/>
+      <c r="M1505" t="inlineStr">
+        <is>
+          <t>하드웨어구매, 설치</t>
+        </is>
+      </c>
+      <c r="N1505" t="inlineStr"/>
+      <c r="O1505" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>케이시스</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr"/>
+      <c r="C1506" t="inlineStr"/>
+      <c r="D1506" t="inlineStr"/>
+      <c r="E1506" t="inlineStr"/>
+      <c r="F1506" t="inlineStr"/>
+      <c r="G1506" t="inlineStr"/>
+      <c r="H1506" t="inlineStr"/>
+      <c r="I1506" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1506" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1506" t="inlineStr"/>
+      <c r="L1506" t="inlineStr"/>
+      <c r="M1506" t="inlineStr"/>
+      <c r="N1506" t="inlineStr"/>
+      <c r="O1506" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>알이엠시스템</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr"/>
+      <c r="C1507" t="inlineStr"/>
+      <c r="D1507" t="inlineStr"/>
+      <c r="E1507" t="inlineStr"/>
+      <c r="F1507" t="inlineStr"/>
+      <c r="G1507" t="inlineStr"/>
+      <c r="H1507" t="inlineStr"/>
+      <c r="I1507" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1507" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1507" t="inlineStr"/>
+      <c r="L1507" t="inlineStr"/>
+      <c r="M1507" t="inlineStr">
+        <is>
+          <t>프로젝터</t>
+        </is>
+      </c>
+      <c r="N1507" t="inlineStr"/>
+      <c r="O1507" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>셀뷰어</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr"/>
+      <c r="C1508" t="inlineStr"/>
+      <c r="D1508" t="inlineStr"/>
+      <c r="E1508" t="inlineStr"/>
+      <c r="F1508" t="inlineStr"/>
+      <c r="G1508" t="inlineStr"/>
+      <c r="H1508" t="inlineStr"/>
+      <c r="I1508" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1508" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1508" t="inlineStr"/>
+      <c r="L1508" t="inlineStr"/>
+      <c r="M1508" t="inlineStr"/>
+      <c r="N1508" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1508" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>헬로그램</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr"/>
+      <c r="C1509" t="inlineStr"/>
+      <c r="D1509" t="inlineStr"/>
+      <c r="E1509" t="inlineStr"/>
+      <c r="F1509" t="inlineStr"/>
+      <c r="G1509" t="inlineStr"/>
+      <c r="H1509" t="inlineStr"/>
+      <c r="I1509" t="inlineStr">
+        <is>
+          <t>하드웨어</t>
+        </is>
+      </c>
+      <c r="J1509" t="inlineStr">
+        <is>
+          <t>협력사(하드웨어)</t>
+        </is>
+      </c>
+      <c r="K1509" t="inlineStr"/>
+      <c r="L1509" t="inlineStr"/>
+      <c r="M1509" t="inlineStr"/>
+      <c r="N1509" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1509" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>팀로지스</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>윤승찬</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr"/>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>010-3442-9911</t>
+        </is>
+      </c>
+      <c r="F1510" t="inlineStr">
+        <is>
+          <t>teamlogis2025@gmail.com</t>
+        </is>
+      </c>
+      <c r="G1510" t="inlineStr"/>
+      <c r="H1510" t="inlineStr">
+        <is>
+          <t>경기도 시흥시 서울대학로 59-69 배돋테크노밸리 328호</t>
+        </is>
+      </c>
+      <c r="I1510" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1510" t="inlineStr">
+        <is>
+          <t>협력사(운송)</t>
+        </is>
+      </c>
+      <c r="K1510" t="inlineStr"/>
+      <c r="L1510" t="inlineStr"/>
+      <c r="M1510" t="inlineStr">
+        <is>
+          <t>하드웨어, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1510" t="inlineStr"/>
+      <c r="O1510" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>골든벨퀵</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>조성호</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr"/>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>1588-4282</t>
+        </is>
+      </c>
+      <c r="F1511" t="inlineStr">
+        <is>
+          <t>chojo51@hanmail.net</t>
+        </is>
+      </c>
+      <c r="G1511" t="inlineStr"/>
+      <c r="H1511" t="inlineStr">
+        <is>
+          <t>서울시 은평구 신사동 200-74(서울,경기전지역배송)</t>
+        </is>
+      </c>
+      <c r="I1511" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1511" t="inlineStr">
+        <is>
+          <t>협력사(운송)</t>
+        </is>
+      </c>
+      <c r="K1511" t="inlineStr"/>
+      <c r="L1511" t="inlineStr"/>
+      <c r="M1511" t="inlineStr">
+        <is>
+          <t>빠른배송, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1511" t="inlineStr">
+        <is>
+          <t>올림 지정업체 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1511" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>Superb AI</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>김종환</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>매니저</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr"/>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>010-2075-9914</t>
+        </is>
+      </c>
+      <c r="F1512" t="inlineStr">
+        <is>
+          <t>jonhwan.kim@superb-ai.com</t>
+        </is>
+      </c>
+      <c r="G1512" t="inlineStr"/>
+      <c r="H1512" t="inlineStr">
+        <is>
+          <t>서울시 강남구 테헤란로 427 18-101</t>
+        </is>
+      </c>
+      <c r="I1512" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1512" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1512" t="inlineStr">
+        <is>
+          <t>내부담당: Andy</t>
+        </is>
+      </c>
+      <c r="L1512" t="inlineStr"/>
+      <c r="M1512" t="inlineStr">
+        <is>
+          <t>웹개발, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1512" t="inlineStr">
+        <is>
+          <t>학습형 AI/ 백/프론트/퍼블리싱</t>
+        </is>
+      </c>
+      <c r="O1512" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>페이버소프트</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr"/>
+      <c r="C1513" t="inlineStr"/>
+      <c r="D1513" t="inlineStr"/>
+      <c r="E1513" t="inlineStr"/>
+      <c r="F1513" t="inlineStr">
+        <is>
+          <t>filter79@naver.com</t>
+        </is>
+      </c>
+      <c r="G1513" t="inlineStr"/>
+      <c r="H1513" t="inlineStr"/>
+      <c r="I1513" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1513" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1513" t="inlineStr"/>
+      <c r="L1513" t="inlineStr"/>
+      <c r="M1513" t="inlineStr">
+        <is>
+          <t>웹개발, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1513" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1513" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>그루브웹</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>이준희</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr"/>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>010-8242-5142</t>
+        </is>
+      </c>
+      <c r="F1514" t="inlineStr">
+        <is>
+          <t>ceo@groove-web.com</t>
+        </is>
+      </c>
+      <c r="G1514" t="inlineStr"/>
+      <c r="H1514" t="inlineStr">
+        <is>
+          <t>서울 마포구 성산동 13-2, 2층</t>
+        </is>
+      </c>
+      <c r="I1514" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1514" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1514" t="inlineStr"/>
+      <c r="L1514" t="inlineStr"/>
+      <c r="M1514" t="inlineStr">
+        <is>
+          <t>웹개발, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1514" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1514" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>유니코어</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr"/>
+      <c r="C1515" t="inlineStr"/>
+      <c r="D1515" t="inlineStr"/>
+      <c r="E1515" t="inlineStr"/>
+      <c r="F1515" t="inlineStr"/>
+      <c r="G1515" t="inlineStr"/>
+      <c r="H1515" t="inlineStr"/>
+      <c r="I1515" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1515" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1515" t="inlineStr"/>
+      <c r="L1515" t="inlineStr"/>
+      <c r="M1515" t="inlineStr">
+        <is>
+          <t>웹개발, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1515" t="inlineStr"/>
+      <c r="O1515" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>코드인디자인</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>심재철</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr"/>
+      <c r="E1516" t="inlineStr">
+        <is>
+          <t>010-2409-4270</t>
+        </is>
+      </c>
+      <c r="F1516" t="inlineStr">
+        <is>
+          <t>ceo@codeindesign.kr</t>
+        </is>
+      </c>
+      <c r="G1516" t="inlineStr"/>
+      <c r="H1516" t="inlineStr">
+        <is>
+          <t>서울시 강남구 테헤란로 70길 14-10 남양빌딩 10층</t>
+        </is>
+      </c>
+      <c r="I1516" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1516" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1516" t="inlineStr"/>
+      <c r="L1516" t="inlineStr"/>
+      <c r="M1516" t="inlineStr">
+        <is>
+          <t>웹개발, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1516" t="inlineStr">
+        <is>
+          <t>백/프론트/퍼블리싱/플랫폼/SaaS/EPR(사내 시스템)/RPA(업무 자동화)/크롤러</t>
+        </is>
+      </c>
+      <c r="O1516" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>옐로펜슬</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>차민석</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr"/>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>010-7368-7241</t>
+        </is>
+      </c>
+      <c r="F1517" t="inlineStr">
+        <is>
+          <t>yellopencil@naver.com</t>
+        </is>
+      </c>
+      <c r="G1517" t="inlineStr"/>
+      <c r="H1517" t="inlineStr">
+        <is>
+          <t>경기도 고양시 덕양구 내유길 26-8, 가동 101호</t>
+        </is>
+      </c>
+      <c r="I1517" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1517" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1517" t="inlineStr"/>
+      <c r="L1517" t="inlineStr"/>
+      <c r="M1517" t="inlineStr">
+        <is>
+          <t>웹개발, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1517" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1517" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>왈라아이시티</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr"/>
+      <c r="C1518" t="inlineStr"/>
+      <c r="D1518" t="inlineStr"/>
+      <c r="E1518" t="inlineStr"/>
+      <c r="F1518" t="inlineStr"/>
+      <c r="G1518" t="inlineStr"/>
+      <c r="H1518" t="inlineStr"/>
+      <c r="I1518" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1518" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1518" t="inlineStr"/>
+      <c r="L1518" t="inlineStr"/>
+      <c r="M1518" t="inlineStr">
+        <is>
+          <t>웹개발, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1518" t="inlineStr"/>
+      <c r="O1518" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>왈라 ICT</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>박유미</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr"/>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>010-8810-5955</t>
+        </is>
+      </c>
+      <c r="F1519" t="inlineStr">
+        <is>
+          <t>ym@wala-ict.com</t>
+        </is>
+      </c>
+      <c r="G1519" t="inlineStr"/>
+      <c r="H1519" t="inlineStr">
+        <is>
+          <t>서울시 강남구 논현로 748 2층</t>
+        </is>
+      </c>
+      <c r="I1519" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1519" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1519" t="inlineStr"/>
+      <c r="L1519" t="inlineStr"/>
+      <c r="M1519" t="inlineStr">
+        <is>
+          <t>웹, 웹개발, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1519" t="inlineStr"/>
+      <c r="O1519" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>이양호</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>이양호</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>유니티 개발</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr"/>
+      <c r="E1520" t="inlineStr">
+        <is>
+          <t>010-7772-0377</t>
+        </is>
+      </c>
+      <c r="F1520" t="inlineStr">
+        <is>
+          <t>devleeyangho@gmail.com</t>
+        </is>
+      </c>
+      <c r="G1520" t="inlineStr"/>
+      <c r="H1520" t="inlineStr"/>
+      <c r="I1520" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1520" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1520" t="inlineStr"/>
+      <c r="L1520" t="inlineStr"/>
+      <c r="M1520" t="inlineStr">
+        <is>
+          <t>웹개발, 개인(프리랜서)</t>
+        </is>
+      </c>
+      <c r="N1520" t="inlineStr"/>
+      <c r="O1520" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>엔엑스웹(더온)</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>김효성</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr"/>
+      <c r="D1521" t="inlineStr"/>
+      <c r="E1521" t="inlineStr">
+        <is>
+          <t>02-2692-4282</t>
+        </is>
+      </c>
+      <c r="F1521" t="inlineStr">
+        <is>
+          <t>webmaster@nxweb.kr</t>
+        </is>
+      </c>
+      <c r="G1521" t="inlineStr"/>
+      <c r="H1521" t="inlineStr">
+        <is>
+          <t>서울 금천구 가산디지털2로 184, 902호(벽산디지털밸리2차)</t>
+        </is>
+      </c>
+      <c r="I1521" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1521" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1521" t="inlineStr"/>
+      <c r="L1521" t="inlineStr"/>
+      <c r="M1521" t="inlineStr">
+        <is>
+          <t>웹, 웹개발, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1521" t="inlineStr">
+        <is>
+          <t>홈페이지 제작, SEO, 이커머스, 브랜딩, UI/UX 컨설팅 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1521" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>프릭스(PRIX)</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr"/>
+      <c r="C1522" t="inlineStr"/>
+      <c r="D1522" t="inlineStr"/>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>02-3478-0711</t>
+        </is>
+      </c>
+      <c r="F1522" t="inlineStr">
+        <is>
+          <t>info@prix.co.kr</t>
+        </is>
+      </c>
+      <c r="G1522" t="inlineStr"/>
+      <c r="H1522" t="inlineStr">
+        <is>
+          <t>서울 서초구 서초대로 127, 혁성빌딩 401호</t>
+        </is>
+      </c>
+      <c r="I1522" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1522" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1522" t="inlineStr"/>
+      <c r="L1522" t="inlineStr"/>
+      <c r="M1522" t="inlineStr">
+        <is>
+          <t>웹, 웹개발, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1522" t="inlineStr">
+        <is>
+          <t>맞춤형(독립형) 웹사이트/쇼핑몰 제작, 유지보수 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1522" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>이펙터(Effector)</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>문성민</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr"/>
+      <c r="D1523" t="inlineStr"/>
+      <c r="E1523" t="inlineStr">
+        <is>
+          <t>070-4353-5885</t>
+        </is>
+      </c>
+      <c r="F1523" t="inlineStr"/>
+      <c r="G1523" t="inlineStr"/>
+      <c r="H1523" t="inlineStr">
+        <is>
+          <t>서울 강남구 학동로38길 14-4</t>
+        </is>
+      </c>
+      <c r="I1523" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1523" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1523" t="inlineStr"/>
+      <c r="L1523" t="inlineStr"/>
+      <c r="M1523" t="inlineStr">
+        <is>
+          <t>웹, 웹개발, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1523" t="inlineStr">
+        <is>
+          <t>브랜딩/웹디자인/웹사이트 제작, 스튜디오 운영 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1523" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>(주)플랜아이</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr"/>
+      <c r="C1524" t="inlineStr"/>
+      <c r="D1524" t="inlineStr"/>
+      <c r="E1524" t="inlineStr">
+        <is>
+          <t>042-934-3508</t>
+        </is>
+      </c>
+      <c r="F1524" t="inlineStr"/>
+      <c r="G1524" t="inlineStr"/>
+      <c r="H1524" t="inlineStr">
+        <is>
+          <t>대전 유성구 문지로 282-10</t>
+        </is>
+      </c>
+      <c r="I1524" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1524" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1524" t="inlineStr"/>
+      <c r="L1524" t="inlineStr"/>
+      <c r="M1524" t="inlineStr">
+        <is>
+          <t>웹, 웹개발, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1524" t="inlineStr">
+        <is>
+          <t>공공·민간 웹·SI, AI 기반 대화형 웹/클라우드 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1524" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>가비아씨엔에스(퍼스트몰)</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>공경원</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr"/>
+      <c r="D1525" t="inlineStr"/>
+      <c r="E1525" t="inlineStr">
+        <is>
+          <t>1544-3270</t>
+        </is>
+      </c>
+      <c r="F1525" t="inlineStr"/>
+      <c r="G1525" t="inlineStr"/>
+      <c r="H1525" t="inlineStr">
+        <is>
+          <t>경기도 과천시 과천대로7나길 34</t>
+        </is>
+      </c>
+      <c r="I1525" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1525" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1525" t="inlineStr"/>
+      <c r="L1525" t="inlineStr"/>
+      <c r="M1525" t="inlineStr">
+        <is>
+          <t>웹, 웹개발, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1525" t="inlineStr">
+        <is>
+          <t>쇼핑몰·SI·맞춤개발, 홈페이지 제작 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1525" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>(주)웹모아</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>임재택</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr"/>
+      <c r="D1526" t="inlineStr"/>
+      <c r="E1526" t="inlineStr">
+        <is>
+          <t>02-544-4456</t>
+        </is>
+      </c>
+      <c r="F1526" t="inlineStr"/>
+      <c r="G1526" t="inlineStr"/>
+      <c r="H1526" t="inlineStr">
+        <is>
+          <t>서울시 금천구 디지털로9길 68, 대륭포스트타워5차 1001호</t>
+        </is>
+      </c>
+      <c r="I1526" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1526" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1526" t="inlineStr"/>
+      <c r="L1526" t="inlineStr"/>
+      <c r="M1526" t="inlineStr">
+        <is>
+          <t>웹, 웹개발, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1526" t="inlineStr">
+        <is>
+          <t>기업 홈페이지/프로그램 개발·운영, 유지보수 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1526" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>디웹스(DWEBS)</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>최명진</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr"/>
+      <c r="D1527" t="inlineStr"/>
+      <c r="E1527" t="inlineStr"/>
+      <c r="F1527" t="inlineStr"/>
+      <c r="G1527" t="inlineStr"/>
+      <c r="H1527" t="inlineStr">
+        <is>
+          <t>서울 금천구 서부샛길 606, 대성디폴리스 A동 1011-2</t>
+        </is>
+      </c>
+      <c r="I1527" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1527" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1527" t="inlineStr"/>
+      <c r="L1527" t="inlineStr"/>
+      <c r="M1527" t="inlineStr">
+        <is>
+          <t>웹, 웹개발, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1527" t="inlineStr">
+        <is>
+          <t>반응형/PC·모바일 홈페이지, 쇼핑몰, 템플릿, 유지보수 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1527" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>유엘디자인(주)</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>배도연</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr"/>
+      <c r="D1528" t="inlineStr"/>
+      <c r="E1528" t="inlineStr">
+        <is>
+          <t>02-6959-8708</t>
+        </is>
+      </c>
+      <c r="F1528" t="inlineStr"/>
+      <c r="G1528" t="inlineStr"/>
+      <c r="H1528" t="inlineStr">
+        <is>
+          <t>서울 강서구 마곡동 800, 마곡나인스퀘어 807~809호</t>
+        </is>
+      </c>
+      <c r="I1528" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1528" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1528" t="inlineStr"/>
+      <c r="L1528" t="inlineStr"/>
+      <c r="M1528" t="inlineStr">
+        <is>
+          <t>웹, 웹개발, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1528" t="inlineStr">
+        <is>
+          <t>기업 홈페이지 제작·유지보수, 디자인/콘텐츠 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1528" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>10page(㈜메일플러그)</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>안현석</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr"/>
+      <c r="D1529" t="inlineStr"/>
+      <c r="E1529" t="inlineStr"/>
+      <c r="F1529" t="inlineStr"/>
+      <c r="G1529" t="inlineStr"/>
+      <c r="H1529" t="inlineStr">
+        <is>
+          <t>서울 강남구 테헤란로78길 16, 8·10층(노벨빌딩)</t>
+        </is>
+      </c>
+      <c r="I1529" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1529" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1529" t="inlineStr"/>
+      <c r="L1529" t="inlineStr"/>
+      <c r="M1529" t="inlineStr">
+        <is>
+          <t>웹, 웹개발, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1529" t="inlineStr">
+        <is>
+          <t>커스터마이즈형 홈페이지 제작 안내 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1529" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>아반디자인</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr"/>
+      <c r="C1530" t="inlineStr"/>
+      <c r="D1530" t="inlineStr"/>
+      <c r="E1530" t="inlineStr">
+        <is>
+          <t>070-4617-3883</t>
+        </is>
+      </c>
+      <c r="F1530" t="inlineStr"/>
+      <c r="G1530" t="inlineStr"/>
+      <c r="H1530" t="inlineStr">
+        <is>
+          <t>서울 강남구 논현로132길 13, 4층 4846호</t>
+        </is>
+      </c>
+      <c r="I1530" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1530" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1530" t="inlineStr"/>
+      <c r="L1530" t="inlineStr"/>
+      <c r="M1530" t="inlineStr">
+        <is>
+          <t>웹, 웹개발, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1530" t="inlineStr">
+        <is>
+          <t>홈페이지·쇼핑몰·모바일웹/앱, 호스팅/유지관리 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1530" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>(주)푸른아이티코리아</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>김기원</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr"/>
+      <c r="D1531" t="inlineStr"/>
+      <c r="E1531" t="inlineStr"/>
+      <c r="F1531" t="inlineStr"/>
+      <c r="G1531" t="inlineStr"/>
+      <c r="H1531" t="inlineStr">
+        <is>
+          <t>서울 양천구 은행정로 33-1, 2층</t>
+        </is>
+      </c>
+      <c r="I1531" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1531" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1531" t="inlineStr"/>
+      <c r="L1531" t="inlineStr"/>
+      <c r="M1531" t="inlineStr">
+        <is>
+          <t>웹, 웹개발, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1531" t="inlineStr">
+        <is>
+          <t>비영리단체/사회적기업 특화 홈페이지 제작 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1531" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>제네시스랩</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>이영복</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr"/>
+      <c r="E1532" t="inlineStr">
+        <is>
+          <t>02-6402-0118</t>
+        </is>
+      </c>
+      <c r="F1532" t="inlineStr">
+        <is>
+          <t>Sales@genesislab.ai</t>
+        </is>
+      </c>
+      <c r="G1532" t="inlineStr"/>
+      <c r="H1532" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 삼일대로 343, 16층</t>
+        </is>
+      </c>
+      <c r="I1532" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1532" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1532" t="inlineStr"/>
+      <c r="L1532" t="inlineStr"/>
+      <c r="M1532" t="inlineStr">
+        <is>
+          <t>AI개발, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1532" t="inlineStr">
+        <is>
+          <t>한국 폴리텍대학교 XR AI 면접 플랫폼 구축 진행 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1532" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>디아트픽셀(주)</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>유인철</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr"/>
+      <c r="E1533" t="inlineStr">
+        <is>
+          <t>010-7467-1711</t>
+        </is>
+      </c>
+      <c r="F1533" t="inlineStr">
+        <is>
+          <t>theartpixel@daum.net</t>
+        </is>
+      </c>
+      <c r="G1533" t="inlineStr"/>
+      <c r="H1533" t="inlineStr">
+        <is>
+          <t>경기 의정부시 서부로720번길 34, 709호</t>
+        </is>
+      </c>
+      <c r="I1533" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1533" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1533" t="inlineStr"/>
+      <c r="L1533" t="inlineStr"/>
+      <c r="M1533" t="inlineStr">
+        <is>
+          <t>분양전문, 웹개발, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1533" t="inlineStr">
+        <is>
+          <t>대전선화, 울산무거 진행 업체 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1533" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>어소트락</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>박민서</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>대표이사</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr"/>
+      <c r="E1534" t="inlineStr">
+        <is>
+          <t>010-9502-7686</t>
+        </is>
+      </c>
+      <c r="F1534" t="inlineStr">
+        <is>
+          <t>ms@assortrock.com</t>
+        </is>
+      </c>
+      <c r="G1534" t="inlineStr"/>
+      <c r="H1534" t="inlineStr">
+        <is>
+          <t>서울시 서초구 사평대로 335, 금성빌딩 4층</t>
+        </is>
+      </c>
+      <c r="I1534" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1534" t="inlineStr">
+        <is>
+          <t>협력사(개발)</t>
+        </is>
+      </c>
+      <c r="K1534" t="inlineStr"/>
+      <c r="L1534" t="inlineStr"/>
+      <c r="M1534" t="inlineStr">
+        <is>
+          <t>MOU, 엔진개발, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1534" t="inlineStr">
+        <is>
+          <t>홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1534" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>코넬아트디자인</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>노지원</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr"/>
+      <c r="E1535" t="inlineStr">
+        <is>
+          <t>010-4859-1638</t>
+        </is>
+      </c>
+      <c r="F1535" t="inlineStr">
+        <is>
+          <t>adroh@cornellart.kr</t>
+        </is>
+      </c>
+      <c r="G1535" t="inlineStr"/>
+      <c r="H1535" t="inlineStr">
+        <is>
+          <t>서울 중구 퇴계로 180-9</t>
+        </is>
+      </c>
+      <c r="I1535" t="inlineStr">
+        <is>
+          <t>대행</t>
+        </is>
+      </c>
+      <c r="J1535" t="inlineStr">
+        <is>
+          <t>협력사(광고대행사)</t>
+        </is>
+      </c>
+      <c r="K1535" t="inlineStr"/>
+      <c r="L1535" t="inlineStr"/>
+      <c r="M1535" t="inlineStr">
+        <is>
+          <t>팝업스토어, 공간디자인, VMD, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1535" t="inlineStr">
+        <is>
+          <t>올리브영 협력업체 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1535" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>브라운웍스</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>김태형</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr"/>
+      <c r="E1536" t="inlineStr">
+        <is>
+          <t>010-7288-0356</t>
+        </is>
+      </c>
+      <c r="F1536" t="inlineStr">
+        <is>
+          <t>taehyeonguy@gmail.com</t>
+        </is>
+      </c>
+      <c r="G1536" t="inlineStr"/>
+      <c r="H1536" t="inlineStr">
+        <is>
+          <t>서울 강남구 영동대로 511 트레이드타워 2104호</t>
+        </is>
+      </c>
+      <c r="I1536" t="inlineStr">
+        <is>
+          <t>대행</t>
+        </is>
+      </c>
+      <c r="J1536" t="inlineStr">
+        <is>
+          <t>협력사(광고대행사)</t>
+        </is>
+      </c>
+      <c r="K1536" t="inlineStr"/>
+      <c r="L1536" t="inlineStr"/>
+      <c r="M1536" t="inlineStr">
+        <is>
+          <t>분양, 건축, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1536" t="inlineStr"/>
+      <c r="O1536" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>두잇컴퍼니</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>이은주</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>매니저</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr"/>
+      <c r="E1537" t="inlineStr">
+        <is>
+          <t>010-8889-9098</t>
+        </is>
+      </c>
+      <c r="F1537" t="inlineStr">
+        <is>
+          <t>ejlee@doitco.com</t>
+        </is>
+      </c>
+      <c r="G1537" t="inlineStr"/>
+      <c r="H1537" t="inlineStr">
+        <is>
+          <t>서울 서강로1길 12-9 수림빌딩 3F</t>
+        </is>
+      </c>
+      <c r="I1537" t="inlineStr">
+        <is>
+          <t>대행</t>
+        </is>
+      </c>
+      <c r="J1537" t="inlineStr">
+        <is>
+          <t>협력사(광고대행사)</t>
+        </is>
+      </c>
+      <c r="K1537" t="inlineStr"/>
+      <c r="L1537" t="inlineStr"/>
+      <c r="M1537" t="inlineStr">
+        <is>
+          <t>여행, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1537" t="inlineStr">
+        <is>
+          <t>코카콜라 담당자 이전 회사 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1537" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>슬로워커</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>김미래</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>디자이너</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr"/>
+      <c r="E1538" t="inlineStr">
+        <is>
+          <t>010-9481-2807</t>
+        </is>
+      </c>
+      <c r="F1538" t="inlineStr">
+        <is>
+          <t>miraii@slowalk.co.kr</t>
+        </is>
+      </c>
+      <c r="G1538" t="inlineStr"/>
+      <c r="H1538" t="inlineStr">
+        <is>
+          <t>서울시 마포구 동교로39길 4-13, 3층</t>
+        </is>
+      </c>
+      <c r="I1538" t="inlineStr">
+        <is>
+          <t>대행</t>
+        </is>
+      </c>
+      <c r="J1538" t="inlineStr">
+        <is>
+          <t>협력사(광고대행사)</t>
+        </is>
+      </c>
+      <c r="K1538" t="inlineStr"/>
+      <c r="L1538" t="inlineStr"/>
+      <c r="M1538" t="inlineStr">
+        <is>
+          <t>광고, 건축, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1538" t="inlineStr">
+        <is>
+          <t>개운산가로주택정비사업 문의 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1538" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>아이지에이 주식회사</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>임대순</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr"/>
+      <c r="E1539" t="inlineStr">
+        <is>
+          <t>010-5315-7060</t>
+        </is>
+      </c>
+      <c r="F1539" t="inlineStr">
+        <is>
+          <t>igamodel@naver.com</t>
+        </is>
+      </c>
+      <c r="G1539" t="inlineStr"/>
+      <c r="H1539" t="inlineStr">
+        <is>
+          <t>서울시 성동구 성수일로11길 11 2층</t>
+        </is>
+      </c>
+      <c r="I1539" t="inlineStr">
+        <is>
+          <t>전시</t>
+        </is>
+      </c>
+      <c r="J1539" t="inlineStr">
+        <is>
+          <t>협력사(기타)</t>
+        </is>
+      </c>
+      <c r="K1539" t="inlineStr"/>
+      <c r="L1539" t="inlineStr"/>
+      <c r="M1539" t="inlineStr">
+        <is>
+          <t>모형, 키오스크앱개발, 모형제작, 국내(개인)</t>
+        </is>
+      </c>
+      <c r="N1539" t="inlineStr">
+        <is>
+          <t>양평 오빈 공동주택 진행업체 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1539" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>유한회사 나오디자인</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>김종일</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr"/>
+      <c r="E1540" t="inlineStr">
+        <is>
+          <t>010-5693-3578</t>
+        </is>
+      </c>
+      <c r="F1540" t="inlineStr">
+        <is>
+          <t>nao-design@naver.com</t>
+        </is>
+      </c>
+      <c r="G1540" t="inlineStr"/>
+      <c r="H1540" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 동남로 6길 41-14, 301호</t>
+        </is>
+      </c>
+      <c r="I1540" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1540" t="inlineStr">
+        <is>
+          <t>협력사(기타)</t>
+        </is>
+      </c>
+      <c r="K1540" t="inlineStr"/>
+      <c r="L1540" t="inlineStr"/>
+      <c r="M1540" t="inlineStr">
+        <is>
+          <t>광고대행업, 광고물제작, 건축, 국내(법인)</t>
+        </is>
+      </c>
+      <c r="N1540" t="inlineStr"/>
+      <c r="O1540" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>로위랩</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr"/>
+      <c r="C1541" t="inlineStr"/>
+      <c r="D1541" t="inlineStr"/>
+      <c r="E1541" t="inlineStr"/>
+      <c r="F1541" t="inlineStr"/>
+      <c r="G1541" t="inlineStr"/>
+      <c r="H1541" t="inlineStr"/>
+      <c r="I1541" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J1541" t="inlineStr">
+        <is>
+          <t>협력사(기타)</t>
+        </is>
+      </c>
+      <c r="K1541" t="inlineStr"/>
+      <c r="L1541" t="inlineStr"/>
+      <c r="M1541" t="inlineStr">
+        <is>
+          <t>광고대행업, 광고물제작</t>
+        </is>
+      </c>
+      <c r="N1541" t="inlineStr">
+        <is>
+          <t>대림 입찰 경쟁자, 저가로 들어가는 업체 / 홈페이지: (링크)</t>
+        </is>
+      </c>
+      <c r="O1541" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
